--- a/data/trans_orig/P13A_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P13A_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según días que sufre dolor de cabeza al mes en 2023</t>
+          <t>Población según cuántos días al mes sufre dolor de cabeza en 2023 (tasa de respuesta: 99,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>7468</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31835</t>
+          <t>32399</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7396</t>
+          <t>6894</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30345</t>
+          <t>31094</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>2272</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26235</t>
+          <t>25390</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>6215</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24475</t>
+          <t>24391</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11127</t>
+          <t>11475</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42074</t>
+          <t>40209</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22331</t>
+          <t>20695</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>61867</t>
+          <t>58729</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>42202</t>
+          <t>43098</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>80431</t>
+          <t>81863</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>97600</t>
+          <t>97599</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>70093</t>
+          <t>72312</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>126678</t>
+          <t>128072</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>324184</t>
+          <t>329469</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>371202</t>
+          <t>372078</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>200883</t>
+          <t>197242</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>244594</t>
+          <t>243421</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>541209</t>
+          <t>542700</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>606859</t>
+          <t>605838</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,16%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13675</t>
+          <t>13483</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16649</t>
+          <t>17662</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,47 +1349,47 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>13253</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>7182</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>23663</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>0,77%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>13253</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>6968</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>24351</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3834</t>
+          <t>3395</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20346</t>
+          <t>20814</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18295</t>
+          <t>17924</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47155</t>
+          <t>47652</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27869</t>
+          <t>27559</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59381</t>
+          <t>59667</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48048</t>
+          <t>50241</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88705</t>
+          <t>90920</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131156</t>
+          <t>133094</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>310697</t>
+          <t>315259</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>195022</t>
+          <t>193626</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>421007</t>
+          <t>423604</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>45,31%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>319385</t>
+          <t>319020</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>361391</t>
+          <t>360226</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>173291</t>
+          <t>163284</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>334391</t>
+          <t>333284</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>464630</t>
+          <t>467770</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>682238</t>
+          <t>682743</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,03%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15633</t>
+          <t>15391</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12070</t>
+          <t>11876</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26005</t>
+          <t>24897</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16546</t>
+          <t>17283</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35076</t>
+          <t>34473</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7862</t>
+          <t>7152</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23809</t>
+          <t>23712</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>20886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>37314</t>
+          <t>38153</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>31777</t>
+          <t>32189</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>54426</t>
+          <t>54734</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>76260</t>
+          <t>75698</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>112095</t>
+          <t>112205</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>133950</t>
+          <t>133003</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>168790</t>
+          <t>168298</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>219276</t>
+          <t>222360</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>270300</t>
+          <t>272994</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>399005</t>
+          <t>399083</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>439043</t>
+          <t>440896</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>322052</t>
+          <t>323191</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>360862</t>
+          <t>360258</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>738473</t>
+          <t>733965</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>790116</t>
+          <t>786056</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,23%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1871</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15852</t>
+          <t>15200</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,82 +2452,82 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>43025</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>32075</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>61184</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>6,05%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>8,61%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>50259</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>28669</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>69270</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>1,79%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>43025</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>31637</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>62164</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>6,05%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>4,45%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>8,75%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>50259</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>28426</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>69044</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9230</t>
+          <t>9299</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42066</t>
+          <t>40647</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35789</t>
+          <t>35081</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57450</t>
+          <t>56886</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>40385</t>
+          <t>41490</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>90680</t>
+          <t>92816</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>61604</t>
+          <t>60434</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>214241</t>
+          <t>211219</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>168325</t>
+          <t>169561</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>219343</t>
+          <t>220977</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,17 +2728,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>343767</t>
+          <t>343768</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>205694</t>
+          <t>208273</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>417783</t>
+          <t>419267</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,25%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>626153</t>
+          <t>629717</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>811185</t>
+          <t>812084</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>398639</t>
+          <t>397140</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>464719</t>
+          <t>467106</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1035287</t>
+          <t>1034341</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1320970</t>
+          <t>1326288</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>83,03%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>5386</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17867</t>
+          <t>17887</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>23292</t>
+          <t>22871</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>38589</t>
+          <t>39083</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>31140</t>
+          <t>31575</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>51954</t>
+          <t>52341</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8812</t>
+          <t>8945</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24461</t>
+          <t>22644</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20271</t>
+          <t>19386</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34459</t>
+          <t>34868</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>32644</t>
+          <t>33285</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>52261</t>
+          <t>53454</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>77380</t>
+          <t>79222</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>110850</t>
+          <t>111714</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>119970</t>
+          <t>119929</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>148004</t>
+          <t>148998</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>204864</t>
+          <t>202581</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>251467</t>
+          <t>249053</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,6%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>419932</t>
+          <t>419528</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>456310</t>
+          <t>455714</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>335055</t>
+          <t>337462</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>368111</t>
+          <t>369719</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>765490</t>
+          <t>767050</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>816994</t>
+          <t>817264</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,17%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>8778</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>6464</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>27886</t>
+          <t>28114</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>8878</t>
+          <t>10048</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>29032</t>
+          <t>30578</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2831</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10363</t>
+          <t>10583</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5959</t>
+          <t>6879</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>32543</t>
+          <t>32432</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>12585</t>
+          <t>13072</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>36120</t>
+          <t>36162</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>42872</t>
+          <t>44661</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>65484</t>
+          <t>65721</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>126735</t>
+          <t>128909</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>477965</t>
+          <t>487089</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>171473</t>
+          <t>172421</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>635897</t>
+          <t>645504</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>66,38%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>289511</t>
+          <t>288924</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>313145</t>
+          <t>311427</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>114340</t>
+          <t>104673</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>425805</t>
+          <t>425296</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>70,04%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>299542</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>743075</t>
+          <t>742810</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,39%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2295</t>
+          <t>2158</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>9551</t>
+          <t>9238</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>13913</t>
+          <t>14102</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>26309</t>
+          <t>26459</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>17308</t>
+          <t>17197</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>31412</t>
+          <t>31161</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2435</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9714</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>18212</t>
+          <t>18148</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>31405</t>
+          <t>31336</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>22155</t>
+          <t>22503</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>36804</t>
+          <t>37680</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>37727</t>
+          <t>38525</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>57822</t>
+          <t>57957</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>100520</t>
+          <t>100616</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>126036</t>
+          <t>126113</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>145281</t>
+          <t>142348</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>177368</t>
+          <t>177174</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>212445</t>
+          <t>212126</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>234237</t>
+          <t>233417</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>252767</t>
+          <t>253701</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>280913</t>
+          <t>281492</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>474104</t>
+          <t>473591</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>507878</t>
+          <t>509784</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,31%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>25102</t>
+          <t>25203</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>51787</t>
+          <t>51393</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>123979</t>
+          <t>123257</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>181294</t>
+          <t>183039</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>158378</t>
+          <t>161946</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>219326</t>
+          <t>223357</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>62767</t>
+          <t>64389</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>109731</t>
+          <t>108457</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>154255</t>
+          <t>154477</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>216058</t>
+          <t>218063</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>232956</t>
+          <t>230145</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>313274</t>
+          <t>313323</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>405602</t>
+          <t>420364</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>602100</t>
+          <t>603837</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>939748</t>
+          <t>943842</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1584187</t>
+          <t>1715778</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1435920</t>
+          <t>1450980</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2281642</t>
+          <t>2217312</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2715355</t>
+          <t>2713849</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2953391</t>
+          <t>2934164</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1779155</t>
+          <t>1681044</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2343231</t>
+          <t>2339168</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>4505642</t>
+          <t>4464031</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>5221174</t>
+          <t>5191148</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,15%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P13A_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P13A_2023-Edad-trans_orig.xlsx
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16480</t>
+          <t>19847</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7468</t>
+          <t>9160</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32399</t>
+          <t>35478</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>16480</t>
+          <t>19847</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6894</t>
+          <t>9416</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31094</t>
+          <t>39092</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>9107</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2272</t>
+          <t>2590</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25390</t>
+          <t>24420</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,22 +873,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12528</t>
+          <t>14625</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>7175</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24391</t>
+          <t>28941</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>22010</t>
+          <t>23732</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11475</t>
+          <t>12659</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40209</t>
+          <t>43125</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>37204</t>
+          <t>41323</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20695</t>
+          <t>24784</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58729</t>
+          <t>63813</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>60395</t>
+          <t>64045</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>43098</t>
+          <t>45440</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>81863</t>
+          <t>84305</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>97599</t>
+          <t>105368</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>72312</t>
+          <t>80616</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>128072</t>
+          <t>136545</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>353301</t>
+          <t>357363</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>329469</t>
+          <t>334094</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>372078</t>
+          <t>375804</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>222050</t>
+          <t>260097</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>197242</t>
+          <t>235014</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>243421</t>
+          <t>280925</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>575351</t>
+          <t>617460</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>542700</t>
+          <t>581336</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>605838</t>
+          <t>648505</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>84,62%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>311453</t>
+          <t>358613</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>311453</t>
+          <t>358613</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>311453</t>
+          <t>358613</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>711440</t>
+          <t>766407</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>711440</t>
+          <t>766407</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>711440</t>
+          <t>766407</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,67 +1294,67 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13483</t>
+          <t>14461</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>10003</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>5228</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>19038</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
           <t>1,05%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>3,18%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>8819</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>3911</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>17662</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>13253</t>
+          <t>15406</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7182</t>
+          <t>8359</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>23663</t>
+          <t>26296</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9514</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20814</t>
+          <t>22452</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>31731</t>
+          <t>31397</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17924</t>
+          <t>21482</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47652</t>
+          <t>45295</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>41246</t>
+          <t>41189</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27559</t>
+          <t>29089</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59667</t>
+          <t>58325</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>67619</t>
+          <t>86394</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50241</t>
+          <t>64299</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90920</t>
+          <t>112849</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>189327</t>
+          <t>131344</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>133094</t>
+          <t>112015</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>315259</t>
+          <t>150812</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>256945</t>
+          <t>217738</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>193626</t>
+          <t>190126</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>423604</t>
+          <t>253088</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>25,9%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>341980</t>
+          <t>375300</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>319020</t>
+          <t>347718</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>360226</t>
+          <t>399091</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>281468</t>
+          <t>327364</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>163284</t>
+          <t>305743</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>333284</t>
+          <t>349586</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>623448</t>
+          <t>702664</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>467770</t>
+          <t>665340</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>682743</t>
+          <t>735210</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>75,25%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>511345</t>
+          <t>500108</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>511345</t>
+          <t>500108</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>511345</t>
+          <t>500108</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>934892</t>
+          <t>976998</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>934892</t>
+          <t>976998</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>934892</t>
+          <t>976998</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6979</t>
+          <t>7122</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2757</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15391</t>
+          <t>15543</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>17660</t>
+          <t>19652</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11876</t>
+          <t>13358</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24897</t>
+          <t>27643</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>24639</t>
+          <t>26774</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17283</t>
+          <t>18092</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34473</t>
+          <t>36901</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13974</t>
+          <t>13743</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7152</t>
+          <t>7798</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23712</t>
+          <t>24588</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,22 +2011,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28508</t>
+          <t>32351</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20886</t>
+          <t>23969</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38153</t>
+          <t>42886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>42482</t>
+          <t>46094</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>32189</t>
+          <t>35144</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>54734</t>
+          <t>59530</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>92500</t>
+          <t>102699</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>75698</t>
+          <t>85905</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>112205</t>
+          <t>124571</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>151228</t>
+          <t>173007</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>133003</t>
+          <t>154648</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>168298</t>
+          <t>193248</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>243727</t>
+          <t>275706</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>222360</t>
+          <t>250062</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>272994</t>
+          <t>306918</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>24,83%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>420523</t>
+          <t>493842</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>399083</t>
+          <t>472047</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>440896</t>
+          <t>512134</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>342032</t>
+          <t>393856</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>323191</t>
+          <t>374075</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>360258</t>
+          <t>415711</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>762555</t>
+          <t>887698</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>733965</t>
+          <t>854825</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>786056</t>
+          <t>918266</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>74,28%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>533975</t>
+          <t>617406</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>533975</t>
+          <t>617406</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>533975</t>
+          <t>617406</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>539428</t>
+          <t>618866</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>539428</t>
+          <t>618866</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>539428</t>
+          <t>618866</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1073403</t>
+          <t>1236272</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1073403</t>
+          <t>1236272</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1073403</t>
+          <t>1236272</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7234</t>
+          <t>7391</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15200</t>
+          <t>15523</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>43025</t>
+          <t>42479</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32075</t>
+          <t>33273</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61184</t>
+          <t>53101</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>50259</t>
+          <t>49870</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28669</t>
+          <t>38815</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>69270</t>
+          <t>63935</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -2545,102 +2545,102 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>26006</t>
+          <t>30443</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9299</t>
+          <t>20013</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40647</t>
+          <t>43817</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>6,26%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>49039</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>39382</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>59835</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>6,68%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>5,37%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>8,15%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>79482</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>65698</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>97267</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>5,54%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t>4,58%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>45629</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>35081</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>56886</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>6,42%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>4,94%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>8,0%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>71635</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>41490</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>92816</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>145411</t>
+          <t>145032</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>60434</t>
+          <t>123678</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>211219</t>
+          <t>169682</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>198357</t>
+          <t>208262</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>169561</t>
+          <t>189501</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>220977</t>
+          <t>227371</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>343768</t>
+          <t>353295</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>208273</t>
+          <t>323846</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>419267</t>
+          <t>383147</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,73%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>708060</t>
+          <t>516653</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>629717</t>
+          <t>491444</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>812084</t>
+          <t>540503</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>423683</t>
+          <t>434246</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>397140</t>
+          <t>413620</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>467106</t>
+          <t>455820</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1131743</t>
+          <t>950900</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1034341</t>
+          <t>922402</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1326288</t>
+          <t>985112</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>68,72%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>886711</t>
+          <t>699519</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>886711</t>
+          <t>699519</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>886711</t>
+          <t>699519</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>710694</t>
+          <t>734026</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>710694</t>
+          <t>734026</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>710694</t>
+          <t>734026</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1597404</t>
+          <t>1433546</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1597404</t>
+          <t>1433546</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1597404</t>
+          <t>1433546</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>10183</t>
+          <t>11016</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5386</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17887</t>
+          <t>18924</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>30418</t>
+          <t>33328</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>22871</t>
+          <t>24809</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>39083</t>
+          <t>43148</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>40601</t>
+          <t>44344</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>31575</t>
+          <t>34676</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>52341</t>
+          <t>56155</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>14838</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8945</t>
+          <t>10411</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22644</t>
+          <t>25465</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>26811</t>
+          <t>29943</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19386</t>
+          <t>22519</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34868</t>
+          <t>38372</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>41648</t>
+          <t>47016</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33285</t>
+          <t>36860</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>53454</t>
+          <t>59584</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>93775</t>
+          <t>97332</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>79222</t>
+          <t>81328</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>111714</t>
+          <t>115793</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>134072</t>
+          <t>152506</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>119929</t>
+          <t>138851</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>148998</t>
+          <t>170746</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>227847</t>
+          <t>249838</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>202581</t>
+          <t>226661</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>249053</t>
+          <t>273866</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,63%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>438805</t>
+          <t>480069</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>419528</t>
+          <t>462107</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>455714</t>
+          <t>497386</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>352942</t>
+          <t>389089</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>337462</t>
+          <t>369621</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>369719</t>
+          <t>404240</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>791748</t>
+          <t>869157</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>767050</t>
+          <t>841820</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>817264</t>
+          <t>894727</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>73,92%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>557601</t>
+          <t>605490</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>557601</t>
+          <t>605490</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>557601</t>
+          <t>605490</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>544243</t>
+          <t>604865</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>544243</t>
+          <t>604865</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>544243</t>
+          <t>604865</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1101844</t>
+          <t>1210355</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1101844</t>
+          <t>1210355</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1101844</t>
+          <t>1210355</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1589</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8778</t>
+          <t>8765</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>16407</t>
+          <t>17681</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6464</t>
+          <t>12698</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28114</t>
+          <t>25648</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>20353</t>
+          <t>21714</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10048</t>
+          <t>15423</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>30578</t>
+          <t>29240</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>5982</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2831</t>
+          <t>2818</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10583</t>
+          <t>11193</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>19359</t>
+          <t>21435</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6879</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>32432</t>
+          <t>29031</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>25340</t>
+          <t>27613</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>13072</t>
+          <t>20895</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>36162</t>
+          <t>35270</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>53469</t>
+          <t>60329</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>44661</t>
+          <t>48944</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>65721</t>
+          <t>74847</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>293579</t>
+          <t>96393</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>128909</t>
+          <t>84143</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>487089</t>
+          <t>109719</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>347048</t>
+          <t>156722</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>172421</t>
+          <t>139386</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>645504</t>
+          <t>175799</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>301772</t>
+          <t>333088</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>288924</t>
+          <t>318528</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>311427</t>
+          <t>344914</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>277906</t>
+          <t>302455</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>104673</t>
+          <t>288601</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>425296</t>
+          <t>317297</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>579678</t>
+          <t>635543</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>299542</t>
+          <t>614385</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>742810</t>
+          <t>653963</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>77,71%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>365168</t>
+          <t>403628</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>365168</t>
+          <t>403628</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>365168</t>
+          <t>403628</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>607251</t>
+          <t>437964</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>607251</t>
+          <t>437964</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>607251</t>
+          <t>437964</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>972419</t>
+          <t>841592</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>972419</t>
+          <t>841592</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>972419</t>
+          <t>841592</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>9238</t>
+          <t>10033</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,22 +4174,22 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>19024</t>
+          <t>21377</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>14102</t>
+          <t>15422</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>26459</t>
+          <t>29596</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>23642</t>
+          <t>26319</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>17197</t>
+          <t>19054</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>31161</t>
+          <t>36477</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>5531</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2573</t>
+          <t>2862</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>10624</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>24077</t>
+          <t>25643</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>18148</t>
+          <t>18705</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>31336</t>
+          <t>33339</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>29061</t>
+          <t>31174</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>22503</t>
+          <t>23425</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>37680</t>
+          <t>39529</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>47604</t>
+          <t>53299</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>38525</t>
+          <t>42596</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>57957</t>
+          <t>65640</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>113238</t>
+          <t>122560</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>100616</t>
+          <t>108743</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>126113</t>
+          <t>137091</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,17 +4435,17 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>160842</t>
+          <t>175859</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>142348</t>
+          <t>158486</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>177174</t>
+          <t>195578</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>223873</t>
+          <t>244517</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>212126</t>
+          <t>230875</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>233417</t>
+          <t>255699</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>267596</t>
+          <t>293095</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>253701</t>
+          <t>277202</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>281492</t>
+          <t>308307</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>491469</t>
+          <t>537613</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>473591</t>
+          <t>516651</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>509784</t>
+          <t>556192</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,14%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>281079</t>
+          <t>308289</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>281079</t>
+          <t>308289</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>281079</t>
+          <t>308289</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>423935</t>
+          <t>462675</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>423935</t>
+          <t>462675</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>423935</t>
+          <t>462675</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>705014</t>
+          <t>770964</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>705014</t>
+          <t>770964</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>705014</t>
+          <t>770964</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>25203</t>
+          <t>29269</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>51393</t>
+          <t>55553</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>151834</t>
+          <t>164366</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>123257</t>
+          <t>142917</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>183039</t>
+          <t>188685</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>189227</t>
+          <t>204275</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>161946</t>
+          <t>177943</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>223357</t>
+          <t>233433</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>84779</t>
+          <t>91867</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>64389</t>
+          <t>73525</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>108457</t>
+          <t>116379</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>188642</t>
+          <t>204432</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>154477</t>
+          <t>182657</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>218063</t>
+          <t>230380</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>273422</t>
+          <t>296299</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>230145</t>
+          <t>264888</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>313323</t>
+          <t>330452</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>537582</t>
+          <t>586408</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>420364</t>
+          <t>539350</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>603837</t>
+          <t>637824</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>1140195</t>
+          <t>948117</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>943842</t>
+          <t>905681</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1715778</t>
+          <t>995157</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>1677777</t>
+          <t>1534525</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1450980</t>
+          <t>1464905</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2217312</t>
+          <t>1598495</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>2788314</t>
+          <t>2800833</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2713849</t>
+          <t>2744798</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2934164</t>
+          <t>2847721</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2167677</t>
+          <t>2400202</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1681044</t>
+          <t>2350329</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2339168</t>
+          <t>2449004</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>4955991</t>
+          <t>5201035</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>4464031</t>
+          <t>5132037</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>5191148</t>
+          <t>5276229</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>72,92%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>3448068</t>
+          <t>3519016</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3448068</t>
+          <t>3519016</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3448068</t>
+          <t>3519016</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>3648348</t>
+          <t>3717118</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3648348</t>
+          <t>3717118</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3648348</t>
+          <t>3717118</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>7096416</t>
+          <t>7236134</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>7096416</t>
+          <t>7236134</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7096416</t>
+          <t>7236134</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
